--- a/Documentation/Short_Product_Plan(SyncMeet-AI)..xlsx
+++ b/Documentation/Short_Product_Plan(SyncMeet-AI)..xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPATIL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPATIL\Pictures\Project\Unique\syncmeet-ai\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACB58D2-5AB8-4FC7-AA24-0B25564AA971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ED8641-724B-46E2-9194-E2B5C775FD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Product Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="132">
   <si>
     <t>Item</t>
   </si>
@@ -100,33 +100,12 @@
     <t>Automate test pipeline in next sprint</t>
   </si>
   <si>
-    <t>Release</t>
-  </si>
-  <si>
     <t>Key Features</t>
   </si>
   <si>
     <t>Dependencies</t>
   </si>
   <si>
-    <t>v1.0</t>
-  </si>
-  <si>
-    <t>v1.1</t>
-  </si>
-  <si>
-    <t>Authentication, Dashboard MVP</t>
-  </si>
-  <si>
-    <t>Analytics export, Notification system</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Requires API upgrade</t>
-  </si>
-  <si>
     <t>On Track</t>
   </si>
   <si>
@@ -145,27 +124,9 @@
     <t>User Story/Requirement</t>
   </si>
   <si>
-    <t>v0.1</t>
-  </si>
-  <si>
-    <t>v0.2</t>
-  </si>
-  <si>
-    <t>v0.3</t>
-  </si>
-  <si>
-    <t>v0.4</t>
-  </si>
-  <si>
-    <t>v0.5</t>
-  </si>
-  <si>
     <t>US3</t>
   </si>
   <si>
-    <t>Yet to Plan</t>
-  </si>
-  <si>
     <t>Net time what will you do differently</t>
   </si>
   <si>
@@ -218,9 +179,6 @@
   </si>
   <si>
     <t>US6</t>
-  </si>
-  <si>
-    <t>Llist Epic Names</t>
   </si>
   <si>
     <r>
@@ -264,9 +222,6 @@
     <t>US7</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
     <t>SyncMeet-AI</t>
   </si>
   <si>
@@ -442,12 +397,95 @@
   <si>
     <t>Dashboard (UI)</t>
   </si>
+  <si>
+    <t>The product development follows an iterative Agile approach, starting with a Minimum Viable Product (MVP) and progressively adding advanced AI features.</t>
+  </si>
+  <si>
+    <t>Release / Timeline</t>
+  </si>
+  <si>
+    <t>Focus Area</t>
+  </si>
+  <si>
+    <t>Week 1–2</t>
+  </si>
+  <si>
+    <t>• Access to MSME business owners / auditors for interviews
+• GST portal documentation (GSTN official docs)
+• Survey tools (Google Forms / Typeform)
+• GitHub repo initialized (https://github.com/chetank23/GST-INVOICE-AI.git)
+• Team onboarding &amp; role alignment</t>
+  </si>
+  <si>
+    <t>Week 3–4</t>
+  </si>
+  <si>
+    <t>Integrate OCR engine to extract data from scanned invoices (PDF/images); validate extraction accuracy</t>
+  </si>
+  <si>
+    <t>OCR &amp; Invoice Parsing Prototype</t>
+  </si>
+  <si>
+    <t>• OCR library: Tesseract OCR or Google Cloud Vision API (API key required)
+• PDF parsing library: PyMuPDF / pdfplumber
+• Sample invoice dataset (PDF, JPG, PNG formats)
+• Python environment with dependencies: pytesseract, Pillow, pdfplumber
+• Cloud storage (AWS S3 / Firebase) for uploaded invoices
+• Week 1–2 research outputs (invoice field definitions)</t>
+  </si>
+  <si>
+    <t>Week 5–6</t>
+  </si>
+  <si>
+    <t>Build rule-based GST compliance validator; implement billing/invoice generation module; mismatch detection logic</t>
+  </si>
+  <si>
+    <t>GST Rule Engine + Billing System</t>
+  </si>
+  <si>
+    <t>• GSTN API access or GST rule documentation (CGST/IGST/SGST rate tables)
+• Week 3–4 OCR output as structured JSON input
+• Database setup (PostgreSQL / Firebase Firestore) for storing invoice records
+• Backend framework (Flask / FastAPI) with REST API endpoints
+• GST rate master data (HSN/SAC code list)
+• Payment gateway SDK (Razorpay / Stripe) for billing module
+• Authentication system (JWT tokens) — from Week 1–2 auth setup</t>
+  </si>
+  <si>
+    <t>Week 7–8</t>
+  </si>
+  <si>
+    <t>Integrate WhatsApp API for invoice sharing &amp; alerts; build analytics dashboard; end-to-end testing &amp; QA</t>
+  </si>
+  <si>
+    <t>WhatsApp Billing Integration + Dashboard + Testing</t>
+  </si>
+  <si>
+    <t>• WhatsApp Business API (Meta Developer account + approved business number)
+• Twilio or 360dialog as WhatsApp messaging provider
+• Week 5–6 GST rule engine &amp; billing APIs (must be stable)
+• Frontend framework (React.js / Flutter) for dashboard
+• Charting library (Chart.js / Recharts) for analytics widgets
+• End-to-end test suite (Pytest / Selenium) setup
+• CI/CD pipeline (GitHub Actions) for automated testing
+• UAT with at least 2–3 MSME customer contacts
+• Deployment environment (AWS EC2 / Heroku / Railway)</t>
+  </si>
+  <si>
+    <t>Build a basic working pipeline (text input → AI processing → output)</t>
+  </si>
+  <si>
+    <t>1. Text-based meeting input (manual transcript)
+2. Basic topic deviation detection
+Basic toxicity detection
+3. Simple UI (input + output display)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -475,6 +513,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -484,7 +537,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -507,17 +560,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -542,6 +607,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,31 +947,31 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>75</v>
+        <v>54</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>76</v>
+        <v>55</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>77</v>
+      <c r="B5" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -904,33 +984,33 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.21875" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.33203125" style="10" customWidth="1"/>
+    <col min="4" max="4" width="73.21875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="21.33203125" style="9" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" customWidth="1"/>
     <col min="8" max="8" width="11.33203125" customWidth="1"/>
-    <col min="9" max="9" width="22.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>70</v>
+      <c r="D1" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -941,60 +1021,60 @@
       <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>63</v>
+      <c r="J1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="8" t="s">
-        <v>62</v>
+      <c r="B2" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="8"/>
+        <v>48</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="7"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>61</v>
+        <v>48</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>79</v>
+      <c r="B3" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>80</v>
+      <c r="D3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
@@ -1005,31 +1085,31 @@
       <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>105</v>
+      <c r="I3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>121</v>
+      <c r="B4" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>83</v>
+      <c r="D4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
@@ -1040,31 +1120,31 @@
       <c r="H4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>107</v>
+      <c r="I4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>122</v>
+        <v>70</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>87</v>
+        <v>71</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1075,31 +1155,31 @@
       <c r="H5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>107</v>
+      <c r="I5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>123</v>
+        <v>99</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>90</v>
+        <v>104</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
@@ -1110,31 +1190,31 @@
       <c r="H6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>107</v>
+      <c r="I6" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>124</v>
+        <v>100</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>93</v>
+        <v>77</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -1145,31 +1225,31 @@
       <c r="H7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>107</v>
+      <c r="I7" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>126</v>
+        <v>101</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>96</v>
+        <v>80</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>16</v>
@@ -1180,31 +1260,31 @@
       <c r="H8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>107</v>
+      <c r="I8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1215,34 +1295,34 @@
       <c r="H9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>107</v>
+      <c r="I9" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>125</v>
+        <v>103</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G10" s="2">
         <v>5</v>
@@ -1250,99 +1330,99 @@
       <c r="H10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>107</v>
+      <c r="I10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="7"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="A14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="9"/>
+      <c r="D15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="4"/>
+      <c r="D16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="9"/>
+        <v>29</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="2:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="9"/>
+        <v>41</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="8"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>57</v>
+        <v>42</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>58</v>
+        <v>43</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D23" s="10" t="s">
-        <v>59</v>
+      <c r="D23" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1353,147 +1433,105 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="B1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="9" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
-    <col min="4" max="4" width="21.21875" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="29.21875" customWidth="1"/>
+    <col min="5" max="5" width="33.88671875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C1" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="B3" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F3" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="96" x14ac:dyDescent="0.3">
+      <c r="B4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="3">
-        <v>45976</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="3">
-        <v>45983</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3">
-        <v>45990</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45997</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="3">
-        <v>46004</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    </row>
+    <row r="5" spans="2:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="B5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="3">
-        <v>46011</v>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="3">
-        <v>46018</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+    </row>
+    <row r="6" spans="2:6" ht="156" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="204" x14ac:dyDescent="0.3">
+      <c r="B7" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1513,12 +1551,12 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1539,7 +1577,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1554,7 +1592,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">

--- a/Documentation/Short_Product_Plan(SyncMeet-AI)..xlsx
+++ b/Documentation/Short_Product_Plan(SyncMeet-AI)..xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MPATIL\Pictures\Project\Unique\syncmeet-ai\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62ED8641-724B-46E2-9194-E2B5C775FD60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD481EF1-FFE0-4E82-B61A-1C1E2E5D1D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Product Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="141">
   <si>
     <t>Item</t>
   </si>
@@ -91,21 +91,9 @@
     <t>Improvements / Action Items</t>
   </si>
   <si>
-    <t>Team collaboration was great</t>
-  </si>
-  <si>
-    <t>Test coverage was low</t>
-  </si>
-  <si>
-    <t>Automate test pipeline in next sprint</t>
-  </si>
-  <si>
     <t>Key Features</t>
   </si>
   <si>
-    <t>Dependencies</t>
-  </si>
-  <si>
     <t>On Track</t>
   </si>
   <si>
@@ -115,9 +103,6 @@
     <t>Could Have</t>
   </si>
   <si>
-    <t>Test Lead</t>
-  </si>
-  <si>
     <t>Test Case (Tasks)</t>
   </si>
   <si>
@@ -125,9 +110,6 @@
   </si>
   <si>
     <t>US3</t>
-  </si>
-  <si>
-    <t>Net time what will you do differently</t>
   </si>
   <si>
     <t>Notes:</t>
@@ -410,66 +392,13 @@
     <t>Week 1–2</t>
   </si>
   <si>
-    <t>• Access to MSME business owners / auditors for interviews
-• GST portal documentation (GSTN official docs)
-• Survey tools (Google Forms / Typeform)
-• GitHub repo initialized (https://github.com/chetank23/GST-INVOICE-AI.git)
-• Team onboarding &amp; role alignment</t>
-  </si>
-  <si>
     <t>Week 3–4</t>
   </si>
   <si>
-    <t>Integrate OCR engine to extract data from scanned invoices (PDF/images); validate extraction accuracy</t>
-  </si>
-  <si>
-    <t>OCR &amp; Invoice Parsing Prototype</t>
-  </si>
-  <si>
-    <t>• OCR library: Tesseract OCR or Google Cloud Vision API (API key required)
-• PDF parsing library: PyMuPDF / pdfplumber
-• Sample invoice dataset (PDF, JPG, PNG formats)
-• Python environment with dependencies: pytesseract, Pillow, pdfplumber
-• Cloud storage (AWS S3 / Firebase) for uploaded invoices
-• Week 1–2 research outputs (invoice field definitions)</t>
-  </si>
-  <si>
     <t>Week 5–6</t>
   </si>
   <si>
-    <t>Build rule-based GST compliance validator; implement billing/invoice generation module; mismatch detection logic</t>
-  </si>
-  <si>
-    <t>GST Rule Engine + Billing System</t>
-  </si>
-  <si>
-    <t>• GSTN API access or GST rule documentation (CGST/IGST/SGST rate tables)
-• Week 3–4 OCR output as structured JSON input
-• Database setup (PostgreSQL / Firebase Firestore) for storing invoice records
-• Backend framework (Flask / FastAPI) with REST API endpoints
-• GST rate master data (HSN/SAC code list)
-• Payment gateway SDK (Razorpay / Stripe) for billing module
-• Authentication system (JWT tokens) — from Week 1–2 auth setup</t>
-  </si>
-  <si>
     <t>Week 7–8</t>
-  </si>
-  <si>
-    <t>Integrate WhatsApp API for invoice sharing &amp; alerts; build analytics dashboard; end-to-end testing &amp; QA</t>
-  </si>
-  <si>
-    <t>WhatsApp Billing Integration + Dashboard + Testing</t>
-  </si>
-  <si>
-    <t>• WhatsApp Business API (Meta Developer account + approved business number)
-• Twilio or 360dialog as WhatsApp messaging provider
-• Week 5–6 GST rule engine &amp; billing APIs (must be stable)
-• Frontend framework (React.js / Flutter) for dashboard
-• Charting library (Chart.js / Recharts) for analytics widgets
-• End-to-end test suite (Pytest / Selenium) setup
-• CI/CD pipeline (GitHub Actions) for automated testing
-• UAT with at least 2–3 MSME customer contacts
-• Deployment environment (AWS EC2 / Heroku / Railway)</t>
   </si>
   <si>
     <t>Build a basic working pipeline (text input → AI processing → output)</t>
@@ -479,6 +408,94 @@
 2. Basic topic deviation detection
 Basic toxicity detection
 3. Simple UI (input + output display)</t>
+  </si>
+  <si>
+    <t>1. Working prototype (text input system)
+2. Initial AI output (deviation + toxicity)</t>
+  </si>
+  <si>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>Make system actually useful</t>
+  </si>
+  <si>
+    <t>1. Action item extraction
+2. Meeting summary generation
+3. Improve NLP model accuracy
+4. Store results in database</t>
+  </si>
+  <si>
+    <t>1. AI extracts tasks
+2. Generates meeting summary
+3. Data stored</t>
+  </si>
+  <si>
+    <t>1. Jira integration (task creation)
+2. Dashboard for insights
+3. Participation analytics (basic)</t>
+  </si>
+  <si>
+    <t>1. Tasks created in Jira
+2. Dashboard working</t>
+  </si>
+  <si>
+    <t>Connect system to real-worldC7 tools</t>
+  </si>
+  <si>
+    <t>Make system smarter &amp; more complete</t>
+  </si>
+  <si>
+    <t>1. Real-time speech-to-text integration
+2. Participation tracking improvement
+3. Performance optimization
+4. Final testing &amp; bug fixes</t>
+  </si>
+  <si>
+    <t>1. Near-final system
+2. Tested MVP</t>
+  </si>
+  <si>
+    <t>1. Successfully conducted real-world surveys by visiting 6 companies and interacting with professionals</t>
+  </si>
+  <si>
+    <t>2. Received positive feedback and appreciation for the proposed product idea</t>
+  </si>
+  <si>
+    <t>3. Clear understanding of real user problems in both academic and corporate environments</t>
+  </si>
+  <si>
+    <t>4. Effective team collaboration with well-defined responsibilities for each subgroup</t>
+  </si>
+  <si>
+    <t>5. Identified key pain points such as lack of structured action tracking and inefficient meeting follow-ups</t>
+  </si>
+  <si>
+    <t>Limited time restricted the number of companies and users that could be surveyed</t>
+  </si>
+  <si>
+    <t>Feedback collected was mostly qualitative and not yet quantitatively analyzed</t>
+  </si>
+  <si>
+    <t>No prototype was available during discussions to demonstrate the concept</t>
+  </si>
+  <si>
+    <t>Some responses were high-level and require deeper technical validation</t>
+  </si>
+  <si>
+    <t>Increase the sample size of users for better validation</t>
+  </si>
+  <si>
+    <t>Convert survey responses into structured data (charts, percentages)</t>
+  </si>
+  <si>
+    <t>Prepare a basic prototype or demo for better user understanding</t>
+  </si>
+  <si>
+    <t>Ask more targeted and technical questions in future interactions</t>
+  </si>
+  <si>
+    <t>Document feedback more systematically for analysis</t>
   </si>
 </sst>
 </file>
@@ -537,7 +554,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -573,11 +590,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -608,6 +638,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -621,13 +654,78 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -638,6 +736,18 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F95ADB0C-57F6-457F-88DB-011714D83C47}" name="Table1" displayName="Table1" ref="A5:C10" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="4" tableBorderDxfId="5">
+  <autoFilter ref="A5:C10" xr:uid="{F95ADB0C-57F6-457F-88DB-011714D83C47}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{34E16F25-1A01-431C-8906-23F0C1892D4A}" name="What Went Well" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{55AB983B-D963-49D3-8E7A-CD80FBFD1A82}" name="What Didn’t Go Well" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{EA3DBADF-5E88-42D0-B8DC-69F31DC10CFF}" name="Improvements / Action Items" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -947,23 +1057,23 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="72" x14ac:dyDescent="0.3">
@@ -971,7 +1081,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1007,10 +1117,10 @@
         <v>6</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>7</v>
@@ -1025,39 +1135,39 @@
         <v>10</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="7" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -1065,16 +1175,16 @@
         <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>15</v>
@@ -1086,13 +1196,13 @@
         <v>17</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
@@ -1100,16 +1210,16 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>15</v>
@@ -1121,30 +1231,30 @@
         <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1156,30 +1266,30 @@
         <v>17</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>15</v>
@@ -1191,30 +1301,30 @@
         <v>17</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -1226,30 +1336,30 @@
         <v>17</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>16</v>
@@ -1261,30 +1371,30 @@
         <v>17</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>15</v>
@@ -1296,33 +1406,33 @@
         <v>17</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2">
         <v>5</v>
@@ -1331,13 +1441,13 @@
         <v>17</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1355,10 +1465,10 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
@@ -1368,7 +1478,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E15" s="8"/>
     </row>
@@ -1377,25 +1487,25 @@
         <v>16</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="2:5" ht="21.6" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E18" s="8"/>
     </row>
@@ -1406,23 +1516,23 @@
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D23" s="9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1445,92 +1555,92 @@
   <sheetData>
     <row r="1" spans="2:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="C1" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="60" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="48" x14ac:dyDescent="0.3">
+      <c r="B5" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="36" x14ac:dyDescent="0.3">
+      <c r="B6" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="48" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" ht="96" x14ac:dyDescent="0.3">
-      <c r="B4" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" ht="132" x14ac:dyDescent="0.3">
-      <c r="B5" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="156" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="C7" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="D7" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" ht="204" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>28</v>
+      <c r="F7" s="15" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1540,98 +1650,92 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:D13"/>
+  <dimension ref="A2:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="57.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="40.44140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+    </row>
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="12" t="s">
+        <v>140</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>